--- a/tumores/7. Glándulas salivales.xlsx
+++ b/tumores/7. Glándulas salivales.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Desktop\Ing.Salud\Practicas hospital ORL\Proyecto Practicas\tumores\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Desktop\Ing.Salud\Practicas hospital ORL\clasificador-tnm-cabeza-cuello\tumores\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C29FAB0D-8F75-47E8-9031-AA436886D789}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24A9960D-4EB4-4727-9AC3-A383AFD7840D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="768" yWindow="768" windowWidth="8520" windowHeight="8880" activeTab="1" xr2:uid="{4CA4EF29-18F6-42B8-89A4-4F1C5D6105C8}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{4CA4EF29-18F6-42B8-89A4-4F1C5D6105C8}"/>
   </bookViews>
   <sheets>
     <sheet name="TNM" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="179" uniqueCount="89">
   <si>
     <t>T</t>
   </si>
@@ -109,12 +109,6 @@
     <t>Ganglio ipsilateral ≤3 cm y ENE-</t>
   </si>
   <si>
-    <t>Multiples ganglios ipsilateral ≤6 cm y ENE-</t>
-  </si>
-  <si>
-    <t>Un ganglio ipsilateral &gt;6 cm y ENE-</t>
-  </si>
-  <si>
     <t>≤3 cm y ENE+, &gt;3 cm pero ≤6 cm y ENE-</t>
   </si>
   <si>
@@ -127,12 +121,6 @@
     <t>Ganglio ipsilateral &gt;3 cm ≤6 cm y ENE-</t>
   </si>
   <si>
-    <t>Múltiples ganglios ipsilaterales ≤6 cm</t>
-  </si>
-  <si>
-    <t>Ganglio ipsilateral &gt;6 cm y ENE-</t>
-  </si>
-  <si>
     <t>M</t>
   </si>
   <si>
@@ -148,12 +136,6 @@
     <t>Tipo</t>
   </si>
   <si>
-    <t>Ganglios contralaterales ≤6 cm</t>
-  </si>
-  <si>
-    <t>Ganglios bilaterales ≤6 cm</t>
-  </si>
-  <si>
     <t>Contralaterales ≤6 cm y ENE-</t>
   </si>
   <si>
@@ -241,30 +223,12 @@
     <t>🟨 N2a: Un ganglio ipsilateral &gt;3 cm pero ≤6 cm y ENE-</t>
   </si>
   <si>
-    <t>🟨N2b: Multiples ganglios ipsilateral ≤6 cm y ENE-</t>
-  </si>
-  <si>
     <t>🟨N2c: Ganglios contralaterales ≤6 cm y ENE-</t>
   </si>
   <si>
     <t>🟨N2c: Ganglios bilaterales ≤6 cm y ENE-</t>
   </si>
   <si>
-    <t>🟦N3a: Un ganglio ipsilateral &gt;6 cm y ENE-</t>
-  </si>
-  <si>
-    <t>🟦 N3b: Un ganglios con ENE+</t>
-  </si>
-  <si>
-    <t>Ganglio linfático con ENE+ </t>
-  </si>
-  <si>
-    <t>🟦N3b: Más de un ganglio con ENE+</t>
-  </si>
-  <si>
-    <t>Ganglios linfáticos con ENE+ </t>
-  </si>
-  <si>
     <t>🟩N1: Un ganglio ipsilateral ≤3 cm y ENE-</t>
   </si>
   <si>
@@ -302,6 +266,33 @@
   </si>
   <si>
     <t>T0, T1, T2, T3, T4a</t>
+  </si>
+  <si>
+    <t>🟨N2b: Múltiples ganglios ipsilateral ≤6 cm y ENE-</t>
+  </si>
+  <si>
+    <t>Ganglio &gt;6 cm y ENE-</t>
+  </si>
+  <si>
+    <t>🟦 N3b: Uno o más ganglios con ENE+</t>
+  </si>
+  <si>
+    <t>Ganglio/s linfáticos con ENE+ </t>
+  </si>
+  <si>
+    <t>Un ganglio &gt;6 cm y ENE-</t>
+  </si>
+  <si>
+    <t>Múltiples ganglios ipsilateral ≤6 cm y ENE-</t>
+  </si>
+  <si>
+    <t>Múltiples ganglios ipsilaterales ≤6 cm y ENE-</t>
+  </si>
+  <si>
+    <t>Ganglios contralaterales ≤6 cm y ENE-</t>
+  </si>
+  <si>
+    <t>Ganglios bilaterales ≤6 cm y ENE-</t>
   </si>
 </sst>
 </file>
@@ -801,7 +792,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{93349F43-C6E5-467C-91F1-9BFB47441F05}">
-  <dimension ref="A1:F29"/>
+  <dimension ref="A1:F28"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9" style="5" bestFit="1" customWidth="1"/>
@@ -818,7 +809,7 @@
         <v>8</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="C1" s="3" t="s">
         <v>9</v>
@@ -827,7 +818,7 @@
         <v>12</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="F1" s="3" t="s">
         <v>10</v>
@@ -839,7 +830,7 @@
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="D2" s="2"/>
       <c r="E2" s="1" t="s">
@@ -855,7 +846,7 @@
       </c>
       <c r="B3" s="2"/>
       <c r="C3" s="2" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="D3" s="2"/>
       <c r="E3" s="2" t="s">
@@ -871,14 +862,14 @@
       </c>
       <c r="B4" s="2"/>
       <c r="C4" s="2" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="D4" s="2"/>
       <c r="E4" s="2" t="s">
         <v>3</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>86</v>
+        <v>74</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
@@ -887,14 +878,14 @@
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="2" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="D5" s="2"/>
       <c r="E5" s="2" t="s">
         <v>4</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>87</v>
+        <v>75</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
@@ -903,14 +894,14 @@
       </c>
       <c r="B6" s="2"/>
       <c r="C6" s="2" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="D6" s="2"/>
       <c r="E6" s="2" t="s">
         <v>5</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>88</v>
+        <v>76</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="72.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
@@ -919,16 +910,16 @@
       </c>
       <c r="B7" s="2"/>
       <c r="C7" s="2" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>7</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>89</v>
+        <v>77</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
@@ -937,16 +928,16 @@
       </c>
       <c r="B8" s="6"/>
       <c r="C8" s="6" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>13</v>
       </c>
       <c r="F8" s="6" t="s">
-        <v>89</v>
+        <v>77</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
@@ -957,7 +948,7 @@
         <v>15</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="E9" s="5" t="s">
         <v>17</v>
@@ -974,13 +965,13 @@
         <v>15</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="E10" s="5" t="s">
         <v>18</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
@@ -991,7 +982,7 @@
         <v>15</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="E11" s="5" t="s">
         <v>19</v>
@@ -1008,13 +999,13 @@
         <v>15</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="E12" s="5" t="s">
         <v>20</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
@@ -1025,14 +1016,14 @@
         <v>15</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>71</v>
+        <v>80</v>
       </c>
       <c r="D13" s="2"/>
       <c r="E13" s="2" t="s">
         <v>21</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>33</v>
+        <v>86</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
@@ -1043,14 +1034,14 @@
         <v>15</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="D14" s="2"/>
       <c r="E14" s="2" t="s">
         <v>22</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>40</v>
+        <v>87</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="22.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -1061,14 +1052,14 @@
         <v>15</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="D15" s="2"/>
       <c r="E15" s="2" t="s">
         <v>22</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>41</v>
+        <v>88</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
@@ -1079,50 +1070,49 @@
         <v>15</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="D16" s="2"/>
       <c r="E16" s="2" t="s">
         <v>23</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>34</v>
+        <v>81</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A17" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="B17" s="2" t="s">
+      <c r="A17" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B17" s="5" t="s">
         <v>15</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="D17" s="2"/>
-      <c r="E17" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="E17" s="5" t="s">
         <v>24</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="B18" s="2" t="s">
-        <v>15</v>
+      <c r="B18" s="11" t="s">
+        <v>16</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>77</v>
+        <v>61</v>
       </c>
       <c r="D18" s="2"/>
       <c r="E18" s="2" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>78</v>
+        <v>25</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
@@ -1133,17 +1123,17 @@
         <v>16</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="D19" s="2"/>
       <c r="E19" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A20" s="5" t="s">
         <v>14</v>
       </c>
@@ -1151,14 +1141,14 @@
         <v>16</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D20" s="2"/>
       <c r="E20" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
     </row>
     <row r="21" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
@@ -1169,14 +1159,16 @@
         <v>16</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="D21" s="2"/>
+        <v>68</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>27</v>
+      </c>
       <c r="E21" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>26</v>
+        <v>69</v>
       </c>
     </row>
     <row r="22" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
@@ -1189,14 +1181,12 @@
       <c r="C22" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="D22" s="2" t="s">
-        <v>29</v>
-      </c>
+      <c r="D22" s="2"/>
       <c r="E22" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
     </row>
     <row r="23" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
@@ -1207,17 +1197,17 @@
         <v>16</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="D23" s="2"/>
       <c r="E23" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A24" s="5" t="s">
         <v>14</v>
       </c>
@@ -1225,100 +1215,82 @@
         <v>16</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="D24" s="2"/>
       <c r="E24" s="2" t="s">
         <v>22</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A25" s="5" t="s">
+      <c r="A25" s="9" t="s">
         <v>14</v>
       </c>
       <c r="B25" s="11" t="s">
         <v>16</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="D25" s="2"/>
       <c r="E25" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A26" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="B26" s="11" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" ht="58.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A26" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="B26" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="C26" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="D26" s="2"/>
-      <c r="E26" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="F26" s="2" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" ht="58.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A27" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="B27" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="C27" s="7" t="s">
-        <v>83</v>
-      </c>
-      <c r="D27" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="E27" s="7" t="s">
+      <c r="C26" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="D26" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="E26" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="F27" s="7" t="s">
+      <c r="F26" s="7" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A27" s="5" t="s">
         <v>31</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="D27" s="2"/>
+      <c r="E27" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="F27" s="2" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A28" s="5" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>84</v>
+        <v>73</v>
       </c>
       <c r="D28" s="2"/>
       <c r="E28" s="2" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A29" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="C29" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="D29" s="2"/>
-      <c r="E29" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="F29" s="2" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
     </row>
   </sheetData>
@@ -1344,10 +1316,10 @@
         <v>14</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
     </row>
     <row r="2" spans="1:4" s="14" customFormat="1" x14ac:dyDescent="0.3">
@@ -1358,7 +1330,7 @@
         <v>18</v>
       </c>
       <c r="C2" s="13" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="D2" s="13">
         <v>0</v>
@@ -1372,10 +1344,10 @@
         <v>18</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
@@ -1386,10 +1358,10 @@
         <v>18</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
@@ -1400,24 +1372,24 @@
         <v>18</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>19</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
@@ -1425,41 +1397,41 @@
         <v>7</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
@@ -1467,27 +1439,27 @@
         <v>13</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
     </row>
   </sheetData>

--- a/tumores/7. Glándulas salivales.xlsx
+++ b/tumores/7. Glándulas salivales.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Desktop\Ing.Salud\Practicas hospital ORL\clasificador-tnm-cabeza-cuello\tumores\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24A9960D-4EB4-4727-9AC3-A383AFD7840D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6114988-AA83-4773-A7D7-E1BE69D4E589}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{4CA4EF29-18F6-42B8-89A4-4F1C5D6105C8}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="179" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="88">
   <si>
     <t>T</t>
   </si>
@@ -199,18 +199,6 @@
     <t>🟦T3: &gt; 4 cm con diseminación extraparenquimatosa</t>
   </si>
   <si>
-    <t xml:space="preserve"> Piel, Mandíbula, Canal auditivo, Nervio facial</t>
-  </si>
-  <si>
-    <t>🟥T4a: Invasión mod. Avanzada *</t>
-  </si>
-  <si>
-    <t>🟥 T4b: Invasión muy avanzada</t>
-  </si>
-  <si>
-    <t>Láminas pterigoideas, Base del cráneo, Atrapamiento de arteria carótida interna</t>
-  </si>
-  <si>
     <t>NX: Ganglios no evaluables</t>
   </si>
   <si>
@@ -259,9 +247,6 @@
     <t>&gt; 4 cm con diseminación extraparenquimatosa</t>
   </si>
   <si>
-    <t>Inv:</t>
-  </si>
-  <si>
     <t>T0, T1, T2, T3</t>
   </si>
   <si>
@@ -293,6 +278,18 @@
   </si>
   <si>
     <t>Ganglios bilaterales ≤6 cm y ENE-</t>
+  </si>
+  <si>
+    <t>🟥T4a: Enfermedad localmente avanzada *</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Invasión de la Piel, Invasión de la Mandíbula, Invasión del Canal auditivo, Invasión del Nervio facial</t>
+  </si>
+  <si>
+    <t>🟥 T4b: Enfermedad localmente muy avanzada *</t>
+  </si>
+  <si>
+    <t>Apófisis pterigoides, Base del cráneo, Envuelve la carótida interna</t>
   </si>
 </sst>
 </file>
@@ -869,7 +866,7 @@
         <v>3</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
@@ -885,7 +882,7 @@
         <v>4</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
@@ -901,7 +898,7 @@
         <v>5</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="72.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
@@ -910,35 +907,31 @@
       </c>
       <c r="B7" s="2"/>
       <c r="C7" s="2" t="s">
-        <v>58</v>
+        <v>84</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>57</v>
+        <v>85</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="F7" s="2" t="s">
-        <v>77</v>
-      </c>
+      <c r="F7" s="2"/>
     </row>
     <row r="8" spans="1:6" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="6" t="s">
         <v>0</v>
       </c>
       <c r="B8" s="6"/>
-      <c r="C8" s="6" t="s">
-        <v>59</v>
+      <c r="C8" s="7" t="s">
+        <v>86</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>60</v>
+        <v>87</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="F8" s="6" t="s">
-        <v>77</v>
-      </c>
+      <c r="F8" s="6"/>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" s="5" t="s">
@@ -948,7 +941,7 @@
         <v>15</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="E9" s="5" t="s">
         <v>17</v>
@@ -965,7 +958,7 @@
         <v>15</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="E10" s="5" t="s">
         <v>18</v>
@@ -982,7 +975,7 @@
         <v>15</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="E11" s="5" t="s">
         <v>19</v>
@@ -999,7 +992,7 @@
         <v>15</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="E12" s="5" t="s">
         <v>20</v>
@@ -1016,14 +1009,14 @@
         <v>15</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="D13" s="2"/>
       <c r="E13" s="2" t="s">
         <v>21</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
@@ -1034,14 +1027,14 @@
         <v>15</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="D14" s="2"/>
       <c r="E14" s="2" t="s">
         <v>22</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="22.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -1052,14 +1045,14 @@
         <v>15</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="D15" s="2"/>
       <c r="E15" s="2" t="s">
         <v>22</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
@@ -1070,14 +1063,14 @@
         <v>15</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="D16" s="2"/>
       <c r="E16" s="2" t="s">
         <v>23</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.3">
@@ -1088,13 +1081,13 @@
         <v>15</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="E17" s="5" t="s">
         <v>24</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
@@ -1105,7 +1098,7 @@
         <v>16</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="D18" s="2"/>
       <c r="E18" s="2" t="s">
@@ -1123,7 +1116,7 @@
         <v>16</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="D19" s="2"/>
       <c r="E19" s="2" t="s">
@@ -1141,7 +1134,7 @@
         <v>16</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="D20" s="2"/>
       <c r="E20" s="2" t="s">
@@ -1159,7 +1152,7 @@
         <v>16</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="D21" s="2" t="s">
         <v>27</v>
@@ -1168,7 +1161,7 @@
         <v>20</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
     </row>
     <row r="22" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
@@ -1179,14 +1172,14 @@
         <v>16</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="D22" s="2"/>
       <c r="E22" s="2" t="s">
         <v>21</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
     </row>
     <row r="23" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
@@ -1197,7 +1190,7 @@
         <v>16</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="D23" s="2"/>
       <c r="E23" s="2" t="s">
@@ -1215,7 +1208,7 @@
         <v>16</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="D24" s="2"/>
       <c r="E24" s="2" t="s">
@@ -1233,14 +1226,14 @@
         <v>16</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="D25" s="2"/>
       <c r="E25" s="2" t="s">
         <v>23</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
     </row>
     <row r="26" spans="1:6" ht="58.2" thickBot="1" x14ac:dyDescent="0.35">
@@ -1251,7 +1244,7 @@
         <v>16</v>
       </c>
       <c r="C26" s="7" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="D26" s="7" t="s">
         <v>38</v>
@@ -1268,7 +1261,7 @@
         <v>31</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="D27" s="2"/>
       <c r="E27" s="2" t="s">
@@ -1283,7 +1276,7 @@
         <v>31</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="D28" s="2"/>
       <c r="E28" s="2" t="s">
@@ -1380,7 +1373,7 @@
     </row>
     <row r="6" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>19</v>
@@ -1408,7 +1401,7 @@
     </row>
     <row r="8" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>50</v>

--- a/tumores/7. Glándulas salivales.xlsx
+++ b/tumores/7. Glándulas salivales.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Desktop\Ing.Salud\Practicas hospital ORL\clasificador-tnm-cabeza-cuello\tumores\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6114988-AA83-4773-A7D7-E1BE69D4E589}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09D40AD3-15B0-445B-A9EF-5AAE2505639F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{4CA4EF29-18F6-42B8-89A4-4F1C5D6105C8}"/>
   </bookViews>
@@ -283,13 +283,13 @@
     <t>🟥T4a: Enfermedad localmente avanzada *</t>
   </si>
   <si>
-    <t xml:space="preserve"> Invasión de la Piel, Invasión de la Mandíbula, Invasión del Canal auditivo, Invasión del Nervio facial</t>
-  </si>
-  <si>
     <t>🟥 T4b: Enfermedad localmente muy avanzada *</t>
   </si>
   <si>
     <t>Apófisis pterigoides, Base del cráneo, Envuelve la carótida interna</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Invasión de la piel, Invasión de mandíbula, Invasión del canal auditivo, Invasión del nervio facial</t>
   </si>
 </sst>
 </file>
@@ -910,7 +910,7 @@
         <v>84</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>7</v>
@@ -923,10 +923,10 @@
       </c>
       <c r="B8" s="6"/>
       <c r="C8" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="D8" s="7" t="s">
         <v>86</v>
-      </c>
-      <c r="D8" s="7" t="s">
-        <v>87</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>13</v>

--- a/tumores/7. Glándulas salivales.xlsx
+++ b/tumores/7. Glándulas salivales.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Desktop\Ing.Salud\Practicas hospital ORL\clasificador-tnm-cabeza-cuello\tumores\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09D40AD3-15B0-445B-A9EF-5AAE2505639F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0BDA9DBE-94E2-4295-BAD5-6C83C360C6B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{4CA4EF29-18F6-42B8-89A4-4F1C5D6105C8}"/>
   </bookViews>
@@ -289,7 +289,7 @@
     <t>Apófisis pterigoides, Base del cráneo, Envuelve la carótida interna</t>
   </si>
   <si>
-    <t xml:space="preserve"> Invasión de la piel, Invasión de mandíbula, Invasión del canal auditivo, Invasión del nervio facial</t>
+    <t xml:space="preserve"> Invasión de la piel, Invasión de mandíbula, Invasión del conducto auditivo, Invasión del nervio facial</t>
   </si>
 </sst>
 </file>
